--- a/jpcore-r4/develop/ValueSet-jp-observation-dental-category-vs.xlsx
+++ b/jpcore-r4/develop/ValueSet-jp-observation-dental-category-vs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="35">
   <si>
     <t>Property</t>
   </si>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>JP Coreにて定義した歯科のObservationリソースに関するカテゴリのコード</t>
+    <t>JP Coreにて定義した歯科のObservationリソースに関するカテゴリの第２コード</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -93,7 +93,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright This material contains content from LOINC (http://loinc.org). LOINC is copyright © 1995-2020, Regenstrief Institute, Inc. and the Logical Observation Identifiers Names and Codes (LOINC) Committee and is available at no cost under the license at http://loinc.org/license. LOINC® is a registered United States trademark of Regenstrief Institute, Inc</t>
   </si>
   <si>
     <t>Immutable</t>
@@ -102,10 +102,13 @@
     <t>BooleanType[null]</t>
   </si>
   <si>
-    <t>Codes</t>
-  </si>
-  <si>
-    <t>All codes</t>
+    <t>Concept</t>
+  </si>
+  <si>
+    <t>LP89803-8</t>
+  </si>
+  <si>
+    <t>歯科</t>
   </si>
   <si>
     <t/>
@@ -114,7 +117,7 @@
     <t>System URI</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/CodeSystem/JP_ObservationDentalCategory_CS</t>
+    <t>http://loinc.org</t>
   </si>
 </sst>
 </file>
@@ -391,26 +394,32 @@
       <c r="A1" t="s" s="1">
         <v>29</v>
       </c>
+      <c r="B1" t="s" s="1">
+        <v>22</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
         <v>30</v>
       </c>
+      <c r="B2" t="s" s="2">
+        <v>31</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/jpcore-r4/develop/ValueSet-jp-observation-dental-category-vs.xlsx
+++ b/jpcore-r4/develop/ValueSet-jp-observation-dental-category-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-31</t>
+    <t>2024-11-18</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/ValueSet-jp-observation-dental-category-vs.xlsx
+++ b/jpcore-r4/develop/ValueSet-jp-observation-dental-category-vs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="34">
   <si>
     <t>Property</t>
   </si>
@@ -102,13 +102,10 @@
     <t>BooleanType[null]</t>
   </si>
   <si>
-    <t>Concept</t>
-  </si>
-  <si>
-    <t>LP89803-8</t>
-  </si>
-  <si>
-    <t>歯科</t>
+    <t>Codes</t>
+  </si>
+  <si>
+    <t>All codes</t>
   </si>
   <si>
     <t/>
@@ -117,7 +114,7 @@
     <t>System URI</t>
   </si>
   <si>
-    <t>http://loinc.org</t>
+    <t>http://jpfhir.jp/fhir/core/CodeSystem/JP_ObservationDentalCategory_CS</t>
   </si>
 </sst>
 </file>
@@ -394,32 +391,26 @@
       <c r="A1" t="s" s="1">
         <v>29</v>
       </c>
-      <c r="B1" t="s" s="1">
-        <v>22</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
         <v>30</v>
       </c>
-      <c r="B2" t="s" s="2">
-        <v>31</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B4" t="s" s="2">
         <v>33</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/jpcore-r4/develop/ValueSet-jp-observation-dental-category-vs.xlsx
+++ b/jpcore-r4/develop/ValueSet-jp-observation-dental-category-vs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="35">
   <si>
     <t>Property</t>
   </si>
@@ -102,10 +102,13 @@
     <t>BooleanType[null]</t>
   </si>
   <si>
-    <t>Codes</t>
-  </si>
-  <si>
-    <t>All codes</t>
+    <t>Concept</t>
+  </si>
+  <si>
+    <t>LP89803-8</t>
+  </si>
+  <si>
+    <t>歯科</t>
   </si>
   <si>
     <t/>
@@ -114,7 +117,7 @@
     <t>System URI</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/CodeSystem/JP_ObservationDentalCategory_CS</t>
+    <t>http://loinc.org</t>
   </si>
 </sst>
 </file>
@@ -391,26 +394,32 @@
       <c r="A1" t="s" s="1">
         <v>29</v>
       </c>
+      <c r="B1" t="s" s="1">
+        <v>22</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
         <v>30</v>
       </c>
+      <c r="B2" t="s" s="2">
+        <v>31</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
